--- a/data/base/Backlog_23.xlsx
+++ b/data/base/Backlog_23.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\netuno\Departamentos\GTI\Governança de TI\Governança Adriano\Backlog\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BDBE01AC-BEDB-4C61-A930-7C741F559028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD0D2802-6DA7-474C-87C0-51CA300E483C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-990" windowWidth="29040" windowHeight="15720" xr2:uid="{F94ADF0D-E689-408D-A963-E639FABAA829}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F94ADF0D-E689-408D-A963-E639FABAA829}"/>
   </bookViews>
   <sheets>
     <sheet name="SPN" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">ITI!$A$1:$K$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">SPN!$A$1:$K$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">SPN!$A$1:$K$26</definedName>
   </definedNames>
   <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
@@ -624,7 +624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05C2F3D6-88A9-4A6C-8904-EE71E1E2FD4B}">
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="6" customWidth="1"/>
@@ -741,12 +741,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C4" s="5">
         <v>2026</v>
@@ -761,10 +761,10 @@
         <v>46192</v>
       </c>
       <c r="G4" s="5">
-        <v>16819</v>
+        <v>18276</v>
       </c>
       <c r="H4" s="12">
-        <v>46157.643171296295</v>
+        <v>46177.708333333336</v>
       </c>
       <c r="I4" s="16">
         <v>46188</v>
@@ -776,12 +776,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5" s="5">
         <v>2026</v>
@@ -796,10 +796,10 @@
         <v>46192</v>
       </c>
       <c r="G5" s="5">
-        <v>18346</v>
+        <v>18485</v>
       </c>
       <c r="H5" s="12">
-        <v>46178.538541666669</v>
+        <v>46181.62840277778</v>
       </c>
       <c r="I5" s="16">
         <v>46188</v>
@@ -811,12 +811,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C6" s="5">
         <v>2026</v>
@@ -831,10 +831,10 @@
         <v>46192</v>
       </c>
       <c r="G6" s="5">
-        <v>18418</v>
+        <v>18593</v>
       </c>
       <c r="H6" s="12">
-        <v>46178.708333333336</v>
+        <v>46184.333379629628</v>
       </c>
       <c r="I6" s="16">
         <v>46188</v>
@@ -842,7 +842,7 @@
       <c r="J6" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="K6" s="10" t="s">
+      <c r="K6" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -851,7 +851,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C7" s="5">
         <v>2026</v>
@@ -866,10 +866,10 @@
         <v>46192</v>
       </c>
       <c r="G7" s="5">
-        <v>18653</v>
+        <v>17252</v>
       </c>
       <c r="H7" s="12">
-        <v>46184.543657407405</v>
+        <v>46163.708333333336</v>
       </c>
       <c r="I7" s="16">
         <v>46188</v>
@@ -886,7 +886,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C8" s="5">
         <v>2026</v>
@@ -901,10 +901,10 @@
         <v>46192</v>
       </c>
       <c r="G8" s="5">
-        <v>18665</v>
+        <v>18006</v>
       </c>
       <c r="H8" s="12">
-        <v>46184.612060185187</v>
+        <v>46175.708333333336</v>
       </c>
       <c r="I8" s="16">
         <v>46188</v>
@@ -921,7 +921,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C9" s="5">
         <v>2026</v>
@@ -936,10 +936,10 @@
         <v>46192</v>
       </c>
       <c r="G9" s="5">
-        <v>18730</v>
+        <v>18333</v>
       </c>
       <c r="H9" s="12">
-        <v>46185.403831018521</v>
+        <v>46178.44940972222</v>
       </c>
       <c r="I9" s="16">
         <v>46188</v>
@@ -947,18 +947,18 @@
       <c r="J9" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="K9" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="5">
+      <c r="B10" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="11">
         <v>2026</v>
       </c>
       <c r="D10" s="10">
@@ -970,11 +970,11 @@
       <c r="F10" s="16">
         <v>46192</v>
       </c>
-      <c r="G10" s="5">
-        <v>18276</v>
+      <c r="G10" s="11">
+        <v>18385</v>
       </c>
       <c r="H10" s="12">
-        <v>46177.708333333336</v>
+        <v>46177.666134259256</v>
       </c>
       <c r="I10" s="16">
         <v>46188</v>
@@ -982,18 +982,18 @@
       <c r="J10" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="K10" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="5">
+      <c r="B11" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="11">
         <v>2026</v>
       </c>
       <c r="D11" s="10">
@@ -1005,11 +1005,11 @@
       <c r="F11" s="16">
         <v>46192</v>
       </c>
-      <c r="G11" s="5">
-        <v>18485</v>
+      <c r="G11" s="11">
+        <v>18403</v>
       </c>
       <c r="H11" s="12">
-        <v>46181.62840277778</v>
+        <v>46178.708333333336</v>
       </c>
       <c r="I11" s="16">
         <v>46188</v>
@@ -1017,7 +1017,7 @@
       <c r="J11" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="K11" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
         <v>3</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C12" s="5">
         <v>2026</v>
@@ -1041,10 +1041,10 @@
         <v>46192</v>
       </c>
       <c r="G12" s="5">
-        <v>18593</v>
+        <v>18434</v>
       </c>
       <c r="H12" s="12">
-        <v>46184.333379629628</v>
+        <v>46181.369317129633</v>
       </c>
       <c r="I12" s="16">
         <v>46188</v>
@@ -1076,10 +1076,10 @@
         <v>46192</v>
       </c>
       <c r="G13" s="5">
-        <v>17252</v>
+        <v>18450</v>
       </c>
       <c r="H13" s="12">
-        <v>46163.708333333336</v>
+        <v>46181.445613425924</v>
       </c>
       <c r="I13" s="16">
         <v>46188</v>
@@ -1111,10 +1111,10 @@
         <v>46192</v>
       </c>
       <c r="G14" s="5">
-        <v>18006</v>
+        <v>18460</v>
       </c>
       <c r="H14" s="12">
-        <v>46175.708333333336</v>
+        <v>46181.507349537038</v>
       </c>
       <c r="I14" s="16">
         <v>46188</v>
@@ -1146,10 +1146,10 @@
         <v>46192</v>
       </c>
       <c r="G15" s="5">
-        <v>18333</v>
+        <v>18489</v>
       </c>
       <c r="H15" s="12">
-        <v>46178.44940972222</v>
+        <v>46181.640405092592</v>
       </c>
       <c r="I15" s="16">
         <v>46188</v>
@@ -1157,18 +1157,18 @@
       <c r="J15" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="K15" s="10" t="s">
+      <c r="K15" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="5">
         <v>2026</v>
       </c>
       <c r="D16" s="10">
@@ -1180,11 +1180,11 @@
       <c r="F16" s="16">
         <v>46192</v>
       </c>
-      <c r="G16" s="11">
-        <v>18385</v>
+      <c r="G16" s="5">
+        <v>18501</v>
       </c>
       <c r="H16" s="12">
-        <v>46177.666134259256</v>
+        <v>46181.686215277776</v>
       </c>
       <c r="I16" s="16">
         <v>46188</v>
@@ -1192,18 +1192,18 @@
       <c r="J16" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="K16" s="10" t="s">
+      <c r="K16" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="5">
         <v>2026</v>
       </c>
       <c r="D17" s="10">
@@ -1215,11 +1215,11 @@
       <c r="F17" s="16">
         <v>46192</v>
       </c>
-      <c r="G17" s="11">
-        <v>18403</v>
+      <c r="G17" s="5">
+        <v>18664</v>
       </c>
       <c r="H17" s="12">
-        <v>46178.708333333336</v>
+        <v>46184.611759259256</v>
       </c>
       <c r="I17" s="16">
         <v>46188</v>
@@ -1227,7 +1227,7 @@
       <c r="J17" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="K17" s="10" t="s">
+      <c r="K17" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1251,10 +1251,10 @@
         <v>46192</v>
       </c>
       <c r="G18" s="5">
-        <v>18434</v>
+        <v>18749</v>
       </c>
       <c r="H18" s="12">
-        <v>46181.369317129633</v>
+        <v>46185.49927083333</v>
       </c>
       <c r="I18" s="16">
         <v>46188</v>
@@ -1286,10 +1286,10 @@
         <v>46192</v>
       </c>
       <c r="G19" s="5">
-        <v>18450</v>
+        <v>18754</v>
       </c>
       <c r="H19" s="12">
-        <v>46181.445613425924</v>
+        <v>46185.554965277777</v>
       </c>
       <c r="I19" s="16">
         <v>46188</v>
@@ -1302,13 +1302,13 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="11">
         <v>2026</v>
       </c>
       <c r="D20" s="10">
@@ -1320,11 +1320,11 @@
       <c r="F20" s="16">
         <v>46192</v>
       </c>
-      <c r="G20" s="5">
-        <v>18460</v>
+      <c r="G20" s="11">
+        <v>18775</v>
       </c>
       <c r="H20" s="12">
-        <v>46181.507349537038</v>
+        <v>46184.678923611114</v>
       </c>
       <c r="I20" s="16">
         <v>46188</v>
@@ -1332,18 +1332,18 @@
       <c r="J20" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="K20" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="11">
         <v>2026</v>
       </c>
       <c r="D21" s="10">
@@ -1355,11 +1355,11 @@
       <c r="F21" s="16">
         <v>46192</v>
       </c>
-      <c r="G21" s="5">
-        <v>18489</v>
+      <c r="G21" s="11">
+        <v>18780</v>
       </c>
       <c r="H21" s="12">
-        <v>46181.640405092592</v>
+        <v>46185.691631944443</v>
       </c>
       <c r="I21" s="16">
         <v>46188</v>
@@ -1367,18 +1367,18 @@
       <c r="J21" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="K21" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="11">
         <v>2026</v>
       </c>
       <c r="D22" s="10">
@@ -1390,11 +1390,11 @@
       <c r="F22" s="16">
         <v>46192</v>
       </c>
-      <c r="G22" s="5">
-        <v>18501</v>
+      <c r="G22" s="11">
+        <v>18783</v>
       </c>
       <c r="H22" s="12">
-        <v>46181.686215277776</v>
+        <v>46185.708333333336</v>
       </c>
       <c r="I22" s="16">
         <v>46188</v>
@@ -1402,7 +1402,7 @@
       <c r="J22" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="K22" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
         <v>3</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C23" s="5">
         <v>2026</v>
@@ -1426,29 +1426,29 @@
         <v>46192</v>
       </c>
       <c r="G23" s="5">
-        <v>18664</v>
+        <v>17965</v>
       </c>
       <c r="H23" s="12">
-        <v>46184.611759259256</v>
+        <v>46182.999988425923</v>
       </c>
       <c r="I23" s="16">
         <v>46188</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="5">
+      <c r="B24" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="11">
         <v>2026</v>
       </c>
       <c r="D24" s="10">
@@ -1460,236 +1460,26 @@
       <c r="F24" s="16">
         <v>46192</v>
       </c>
-      <c r="G24" s="5">
-        <v>18749</v>
+      <c r="G24" s="11">
+        <v>18885</v>
       </c>
       <c r="H24" s="12">
-        <v>46185.49927083333</v>
+        <v>46188.583333333336</v>
       </c>
       <c r="I24" s="16">
         <v>46188</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" s="5">
-        <v>2026</v>
-      </c>
-      <c r="D25" s="10">
-        <v>23</v>
-      </c>
-      <c r="E25" s="16">
-        <v>46188</v>
-      </c>
-      <c r="F25" s="16">
-        <v>46192</v>
-      </c>
-      <c r="G25" s="5">
-        <v>18754</v>
-      </c>
-      <c r="H25" s="12">
-        <v>46185.554965277777</v>
-      </c>
-      <c r="I25" s="16">
-        <v>46188</v>
-      </c>
-      <c r="J25" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C26" s="11">
-        <v>2026</v>
-      </c>
-      <c r="D26" s="10">
-        <v>23</v>
-      </c>
-      <c r="E26" s="16">
-        <v>46188</v>
-      </c>
-      <c r="F26" s="16">
-        <v>46192</v>
-      </c>
-      <c r="G26" s="11">
-        <v>18775</v>
-      </c>
-      <c r="H26" s="12">
-        <v>46184.678923611114</v>
-      </c>
-      <c r="I26" s="16">
-        <v>46188</v>
-      </c>
-      <c r="J26" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="K26" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" s="11">
-        <v>2026</v>
-      </c>
-      <c r="D27" s="10">
-        <v>23</v>
-      </c>
-      <c r="E27" s="16">
-        <v>46188</v>
-      </c>
-      <c r="F27" s="16">
-        <v>46192</v>
-      </c>
-      <c r="G27" s="11">
-        <v>18780</v>
-      </c>
-      <c r="H27" s="12">
-        <v>46185.691631944443</v>
-      </c>
-      <c r="I27" s="16">
-        <v>46188</v>
-      </c>
-      <c r="J27" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="K27" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C28" s="11">
-        <v>2026</v>
-      </c>
-      <c r="D28" s="10">
-        <v>23</v>
-      </c>
-      <c r="E28" s="16">
-        <v>46188</v>
-      </c>
-      <c r="F28" s="16">
-        <v>46192</v>
-      </c>
-      <c r="G28" s="11">
-        <v>18783</v>
-      </c>
-      <c r="H28" s="12">
-        <v>46185.708333333336</v>
-      </c>
-      <c r="I28" s="16">
-        <v>46188</v>
-      </c>
-      <c r="J28" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="K28" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C29" s="5">
-        <v>2026</v>
-      </c>
-      <c r="D29" s="10">
-        <v>23</v>
-      </c>
-      <c r="E29" s="16">
-        <v>46188</v>
-      </c>
-      <c r="F29" s="16">
-        <v>46192</v>
-      </c>
-      <c r="G29" s="5">
-        <v>17965</v>
-      </c>
-      <c r="H29" s="12">
-        <v>46182.999988425923</v>
-      </c>
-      <c r="I29" s="16">
-        <v>46188</v>
-      </c>
-      <c r="J29" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="K29" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C30" s="11">
-        <v>2026</v>
-      </c>
-      <c r="D30" s="10">
-        <v>23</v>
-      </c>
-      <c r="E30" s="16">
-        <v>46188</v>
-      </c>
-      <c r="F30" s="16">
-        <v>46192</v>
-      </c>
-      <c r="G30" s="11">
-        <v>18885</v>
-      </c>
-      <c r="H30" s="12">
-        <v>46188.583333333336</v>
-      </c>
-      <c r="I30" s="16">
-        <v>46188</v>
-      </c>
-      <c r="J30" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K30" s="10" t="s">
+      <c r="K24" s="10" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K32" xr:uid="{05C2F3D6-88A9-4A6C-8904-EE71E1E2FD4B}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K30">
-      <sortCondition ref="B1:B32"/>
+  <autoFilter ref="A1:K26" xr:uid="{05C2F3D6-88A9-4A6C-8904-EE71E1E2FD4B}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K24">
+      <sortCondition ref="B1:B26"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -1699,7 +1489,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A01383FE-69B8-4AB3-AF26-C199A6A7A8A1}">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="9" bestFit="1" customWidth="1"/>
@@ -2661,6 +2451,216 @@
         <v>1</v>
       </c>
     </row>
+    <row r="28" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D28" s="10">
+        <v>23</v>
+      </c>
+      <c r="E28" s="16">
+        <v>46188</v>
+      </c>
+      <c r="F28" s="16">
+        <v>46192</v>
+      </c>
+      <c r="G28" s="5">
+        <v>16819</v>
+      </c>
+      <c r="H28" s="12">
+        <v>46157.643171296295</v>
+      </c>
+      <c r="I28" s="16">
+        <v>46188</v>
+      </c>
+      <c r="J28" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D29" s="10">
+        <v>23</v>
+      </c>
+      <c r="E29" s="16">
+        <v>46188</v>
+      </c>
+      <c r="F29" s="16">
+        <v>46192</v>
+      </c>
+      <c r="G29" s="5">
+        <v>18346</v>
+      </c>
+      <c r="H29" s="12">
+        <v>46178.538541666669</v>
+      </c>
+      <c r="I29" s="16">
+        <v>46188</v>
+      </c>
+      <c r="J29" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D30" s="10">
+        <v>23</v>
+      </c>
+      <c r="E30" s="16">
+        <v>46188</v>
+      </c>
+      <c r="F30" s="16">
+        <v>46192</v>
+      </c>
+      <c r="G30" s="5">
+        <v>18418</v>
+      </c>
+      <c r="H30" s="12">
+        <v>46178.708333333336</v>
+      </c>
+      <c r="I30" s="16">
+        <v>46188</v>
+      </c>
+      <c r="J30" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="K30" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D31" s="10">
+        <v>23</v>
+      </c>
+      <c r="E31" s="16">
+        <v>46188</v>
+      </c>
+      <c r="F31" s="16">
+        <v>46192</v>
+      </c>
+      <c r="G31" s="5">
+        <v>18653</v>
+      </c>
+      <c r="H31" s="12">
+        <v>46184.543657407405</v>
+      </c>
+      <c r="I31" s="16">
+        <v>46188</v>
+      </c>
+      <c r="J31" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D32" s="10">
+        <v>23</v>
+      </c>
+      <c r="E32" s="16">
+        <v>46188</v>
+      </c>
+      <c r="F32" s="16">
+        <v>46192</v>
+      </c>
+      <c r="G32" s="5">
+        <v>18665</v>
+      </c>
+      <c r="H32" s="12">
+        <v>46184.612060185187</v>
+      </c>
+      <c r="I32" s="16">
+        <v>46188</v>
+      </c>
+      <c r="J32" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D33" s="10">
+        <v>23</v>
+      </c>
+      <c r="E33" s="16">
+        <v>46188</v>
+      </c>
+      <c r="F33" s="16">
+        <v>46192</v>
+      </c>
+      <c r="G33" s="5">
+        <v>18730</v>
+      </c>
+      <c r="H33" s="12">
+        <v>46185.403831018521</v>
+      </c>
+      <c r="I33" s="16">
+        <v>46188</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K27" xr:uid="{A01383FE-69B8-4AB3-AF26-C199A6A7A8A1}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K27">
